--- a/world_info/scraper/history_table.xlsx
+++ b/world_info/scraper/history_table.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1386"/>
+  <dimension ref="A1:O1406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80285,7 +80285,6 @@
       <c r="J1386" t="n">
         <v>0</v>
       </c>
-      <c r="K1386" t="inlineStr"/>
       <c r="L1386" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -80296,8 +80295,1148 @@
           <t>841天</t>
         </is>
       </c>
-      <c r="N1386" t="inlineStr"/>
-      <c r="O1386" t="inlineStr"/>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Beyond Gravity ˸ An Interplanetary Travel Showcase</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>wrld_660d90dd-2a8e-4743-9b70-1c6237f8192b</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>2026-04-03T15:25:35.598Z</t>
+        </is>
+      </c>
+      <c r="F1387" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1387" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1387" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1387" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>SpeedStar Paradise （StarSight Mt․觀星山 CVS2）</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>wrld_c0f03f3e-ca4c-48cb-8aea-14ed13c1ee03</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>2025-11-17T14:03:16.240Z</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>2026-02-21T14:40:32.411Z</t>
+        </is>
+      </c>
+      <c r="F1388" t="n">
+        <v>1267</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1388" t="n">
+        <v>46</v>
+      </c>
+      <c r="I1388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1388" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1388" t="inlineStr">
+        <is>
+          <t>4天</t>
+        </is>
+      </c>
+      <c r="L1388" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="M1388" t="inlineStr">
+        <is>
+          <t>41天</t>
+        </is>
+      </c>
+      <c r="N1388" t="inlineStr">
+        <is>
+          <t>137天</t>
+        </is>
+      </c>
+      <c r="O1388" t="n">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Project Origin v1․0 Hangout and chill ǃ （Minecraft Build Project）</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>wrld_fb9540f8-68f1-42e8-9430-558fc2d568c4</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>2023-10-15T12:21:09.717Z</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>2025-11-12T15:28:46.998Z</t>
+        </is>
+      </c>
+      <c r="F1389" t="n">
+        <v>4807</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1389" t="n">
+        <v>189</v>
+      </c>
+      <c r="I1389" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1389" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1389" t="inlineStr">
+        <is>
+          <t>5天</t>
+        </is>
+      </c>
+      <c r="L1389" t="inlineStr">
+        <is>
+          <t>3.93%</t>
+        </is>
+      </c>
+      <c r="M1389" t="inlineStr">
+        <is>
+          <t>142天</t>
+        </is>
+      </c>
+      <c r="N1389" t="inlineStr">
+        <is>
+          <t>901天</t>
+        </is>
+      </c>
+      <c r="O1389" t="n">
+        <v>5.34</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Starsight Museum</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>wrld_befc82b9-48d1-4d2a-8269-fb1ac1518f69</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>2025-08-13T13:48:58.458Z</t>
+        </is>
+      </c>
+      <c r="F1390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1390" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1390" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1390" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1390" t="inlineStr">
+        <is>
+          <t>233天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>wrld_44e2cf46-b090-4c70-b5ba-9f7e7ec89d4f</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>2025-08-09T16:53:49.952Z</t>
+        </is>
+      </c>
+      <c r="F1391" t="n">
+        <v>74</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1391" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1391" t="inlineStr">
+        <is>
+          <t>236天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge CVS2 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>wrld_c4d985d3-11de-4a89-9e8b-60b0342a1676</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>2025-05-03T22:35:59.524Z</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>2025-08-02T09:39:48.354Z</t>
+        </is>
+      </c>
+      <c r="F1392" t="n">
+        <v>3578</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1392" t="n">
+        <v>146</v>
+      </c>
+      <c r="I1392" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1392" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1392" t="inlineStr">
+        <is>
+          <t>12天</t>
+        </is>
+      </c>
+      <c r="L1392" t="inlineStr">
+        <is>
+          <t>4.08%</t>
+        </is>
+      </c>
+      <c r="M1392" t="inlineStr">
+        <is>
+          <t>244天</t>
+        </is>
+      </c>
+      <c r="N1392" t="inlineStr">
+        <is>
+          <t>334天</t>
+        </is>
+      </c>
+      <c r="O1392" t="n">
+        <v>10.71</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>StarRiver Space Program v0․1․1 LiftOff</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>wrld_f3acb654-f2ab-49aa-9108-d261c53c5d64</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>2025-07-13T11:38:02.242Z</t>
+        </is>
+      </c>
+      <c r="F1393" t="n">
+        <v>62</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1393" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1393" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1393" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="M1393" t="inlineStr">
+        <is>
+          <t>264天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T SunMoonLake 日月潭 南投山道</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>wrld_1b189721-fa5d-4c64-a24b-9a2c5b89b3b5</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>2025-07-06T07:24:59.566Z</t>
+        </is>
+      </c>
+      <c r="F1394" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1394" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1394" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1394" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1394" t="inlineStr">
+        <is>
+          <t>271天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>UNFINISHED Project T WuLing 武嶺（佐久間峠） 合歡山山道</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>wrld_5fb84156-598a-43c8-8a2b-2c9aa7c95b40</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>2025-07-03T13:07:32.404Z</t>
+        </is>
+      </c>
+      <c r="F1395" t="n">
+        <v>69</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1395" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1395" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1395" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="M1395" t="inlineStr">
+        <is>
+          <t>274天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Project T 9 Turns Taiwan Touge Sacc 九彎十八拐</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>wrld_a6f9cdae-d393-4572-b019-015e4ec6eb35</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>2025-04-09T11:56:42.006Z</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>2025-05-27T15:40:33.056Z</t>
+        </is>
+      </c>
+      <c r="F1396" t="n">
+        <v>915</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1396" t="n">
+        <v>72</v>
+      </c>
+      <c r="I1396" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1396" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1396" t="inlineStr">
+        <is>
+          <t>15天</t>
+        </is>
+      </c>
+      <c r="L1396" t="inlineStr">
+        <is>
+          <t>7.87%</t>
+        </is>
+      </c>
+      <c r="M1396" t="inlineStr">
+        <is>
+          <t>310天</t>
+        </is>
+      </c>
+      <c r="N1396" t="inlineStr">
+        <is>
+          <t>359天</t>
+        </is>
+      </c>
+      <c r="O1396" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>日月潭外周道 Sun Moon Lake</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>wrld_6e465490-9b15-4d2b-b4fe-1ea06e09e55a</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>2025-05-17T13:55:05.489Z</t>
+        </is>
+      </c>
+      <c r="F1397" t="n">
+        <v>79</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1397" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1397" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1397" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="M1397" t="inlineStr">
+        <is>
+          <t>321天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>星門廣場StarGATE Exhibition</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>wrld_16498412-b9e0-404c-9da7-114484c89ecd</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>2024-07-22T05:06:07.749Z</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>2025-05-08T16:46:38.069Z</t>
+        </is>
+      </c>
+      <c r="F1398" t="n">
+        <v>823</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1398" t="n">
+        <v>18</v>
+      </c>
+      <c r="I1398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1398" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1398" t="inlineStr">
+        <is>
+          <t>24天</t>
+        </is>
+      </c>
+      <c r="L1398" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="M1398" t="inlineStr">
+        <is>
+          <t>329天</t>
+        </is>
+      </c>
+      <c r="N1398" t="inlineStr">
+        <is>
+          <t>620天</t>
+        </is>
+      </c>
+      <c r="O1398" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Iseri Nina's Room （Girls Band Cry）</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>wrld_014b19d4-10fc-448d-aaf4-100067cc8eb2</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>2025-12-15T07:34:25.776Z</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>2025-04-10T13:03:37.715Z</t>
+        </is>
+      </c>
+      <c r="F1399" t="n">
+        <v>503</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1399" t="n">
+        <v>69</v>
+      </c>
+      <c r="I1399" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1399" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1399" t="inlineStr">
+        <is>
+          <t>258天</t>
+        </is>
+      </c>
+      <c r="L1399" t="inlineStr">
+        <is>
+          <t>13.72%</t>
+        </is>
+      </c>
+      <c r="M1399" t="inlineStr">
+        <is>
+          <t>358天</t>
+        </is>
+      </c>
+      <c r="N1399" t="inlineStr">
+        <is>
+          <t>109天</t>
+        </is>
+      </c>
+      <c r="O1399" t="n">
+        <v>4.61</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Metro Formosa Test</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>wrld_39eab7ef-be49-4bb2-bb63-56bc30200b82</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>2024-11-24T13:59:30.261Z</t>
+        </is>
+      </c>
+      <c r="F1400" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1400" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1400" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1400" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1400" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1400" t="inlineStr">
+        <is>
+          <t>495天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Taipei MRT 大坪林站 by StarRiver（未完成）</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>wrld_b7193f7d-4616-4b3e-8236-e2f4c7da2d8d</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>2024-09-15T05:18:23.226Z</t>
+        </is>
+      </c>
+      <c r="F1401" t="n">
+        <v>133</v>
+      </c>
+      <c r="G1401" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1401" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1401" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1401" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="M1401" t="inlineStr">
+        <is>
+          <t>565天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Free Trajectory -A Landscape Recreation Experience</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>wrld_81e98a0f-b8eb-4a9b-b01b-35d26758c41c</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>2024-07-23T14:43:36.014Z</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>2024-07-22T19:52:03.599Z</t>
+        </is>
+      </c>
+      <c r="F1402" t="n">
+        <v>373</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1402" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1402" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1402" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1402" t="inlineStr">
+        <is>
+          <t>0天</t>
+        </is>
+      </c>
+      <c r="L1402" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="M1402" t="inlineStr">
+        <is>
+          <t>619天</t>
+        </is>
+      </c>
+      <c r="N1402" t="inlineStr">
+        <is>
+          <t>619天</t>
+        </is>
+      </c>
+      <c r="O1402" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Project：Hide＆Seek LAB（UNFINISHED ）</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>wrld_bac386e9-a543-48e7-a12d-fe9bd3521493</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>2024-07-11T09:44:06.067Z</t>
+        </is>
+      </c>
+      <c r="F1403" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1403" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1403" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1403" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1403" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1403" t="inlineStr">
+        <is>
+          <t>631天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Simple Green Room（Quest 3 MR）</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>wrld_14e668e2-f41b-4655-9440-51be3be0ae81</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>2024-07-08T21:05:28.545Z</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>2024-07-11T08:38:23.384Z</t>
+        </is>
+      </c>
+      <c r="F1404" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G1404" t="n">
+        <v>8</v>
+      </c>
+      <c r="H1404" t="n">
+        <v>52</v>
+      </c>
+      <c r="I1404" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1404" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1404" t="inlineStr">
+        <is>
+          <t>263天</t>
+        </is>
+      </c>
+      <c r="L1404" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="M1404" t="inlineStr">
+        <is>
+          <t>631天</t>
+        </is>
+      </c>
+      <c r="N1404" t="inlineStr">
+        <is>
+          <t>633天</t>
+        </is>
+      </c>
+      <c r="O1404" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Ruined斷垣殘壁 （測試）</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>wrld_7d7a9a66-df6a-4e2c-96fb-19b4dc53c430</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>2024-06-04T16:33:51.575Z</t>
+        </is>
+      </c>
+      <c r="F1405" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1405" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1405" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1405" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1405" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1405" t="inlineStr">
+        <is>
+          <t>667天</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026/04/03</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Project˸ Taiwan</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>wrld_2e5e73d8-758f-4e2d-87db-7770762d52f0</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>2023-12-08T22:31:41.588Z</t>
+        </is>
+      </c>
+      <c r="F1406" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1406" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1406" t="inlineStr"/>
+      <c r="L1406" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M1406" t="inlineStr">
+        <is>
+          <t>846天</t>
+        </is>
+      </c>
+      <c r="N1406" t="inlineStr"/>
+      <c r="O1406" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
